--- a/Formato Matriz de requisitos.xlsx
+++ b/Formato Matriz de requisitos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emacr\Desktop\Proyecto\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4354DDD6-0471-49D2-BF27-F630C07B9123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED75139-3198-4AA0-88BC-E569F29D2299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" RF" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="183">
   <si>
     <t>Fecha de la Versión:</t>
   </si>
@@ -389,9 +389,6 @@
     <t>1.6</t>
   </si>
   <si>
-    <t>Permitir filtrar los resultados por tipo de estacionamiento (calle, cubierto, privado, etc.).</t>
-  </si>
-  <si>
     <t>Seleccionar un estacionamiento y reservar un espacio.</t>
   </si>
   <si>
@@ -407,25 +404,10 @@
     <t>1.10</t>
   </si>
   <si>
-    <t>Indicar la hora de llegada estimada.</t>
-  </si>
-  <si>
     <t>Opción de cancelar la reserva con anticipación.</t>
   </si>
   <si>
     <t xml:space="preserve">Recibir una confirmación de reserva con detalles </t>
-  </si>
-  <si>
-    <t>Pago</t>
-  </si>
-  <si>
-    <t>Integrar métodos de pago seguros (tarjeta de crédito, billeteras digitales, etc.).</t>
-  </si>
-  <si>
-    <t>Calcular el costo del estacionamiento según el tiempo de reserva.</t>
-  </si>
-  <si>
-    <t>Generar recibos de pago.</t>
   </si>
   <si>
     <t>1.11</t>
@@ -434,28 +416,10 @@
     <t>1.12</t>
   </si>
   <si>
-    <t>1.13</t>
-  </si>
-  <si>
     <t>Notificaciones</t>
   </si>
   <si>
-    <t>Recordar al usuario su reserva próxima</t>
-  </si>
-  <si>
-    <t>Enviar notificaciones sobre cambios en la disponibilidad del estacionamiento.</t>
-  </si>
-  <si>
     <t>Alertar sobre el tiempo restante de la reserva.</t>
-  </si>
-  <si>
-    <t>1.14</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
-    <t>1.16</t>
   </si>
   <si>
     <t>Perfil de Usuario</t>
@@ -465,12 +429,6 @@
   </si>
   <si>
     <t>Guardar estacionamientos favoritos.</t>
-  </si>
-  <si>
-    <t>1.17</t>
-  </si>
-  <si>
-    <t>1.18</t>
   </si>
   <si>
     <t>Administración (Para Propietarios de Estacionamientos):</t>
@@ -486,18 +444,6 @@
   </si>
   <si>
     <t>Ver reportes de ocupación y ganancias.</t>
-  </si>
-  <si>
-    <t>1.19</t>
-  </si>
-  <si>
-    <t>1.20</t>
-  </si>
-  <si>
-    <t>1.21</t>
-  </si>
-  <si>
-    <t>1.22</t>
   </si>
   <si>
     <t>Módulo - Apartados</t>
@@ -543,18 +489,6 @@
   </si>
   <si>
     <t>R.1.12</t>
-  </si>
-  <si>
-    <t>R.1.13</t>
-  </si>
-  <si>
-    <t>R.1.14</t>
-  </si>
-  <si>
-    <t>R.1.15</t>
-  </si>
-  <si>
-    <t>R.1.16</t>
   </si>
   <si>
     <t>R.1.17</t>
@@ -611,18 +545,6 @@
     <t>Los usuarios deben poder cancelar su reserva hasta 1 hora antes de la hora de llegada estimada sin penalización. Cancelaciones posteriores pueden estar sujetas a un cargo del 50% del costo de la reserva.</t>
   </si>
   <si>
-    <t>El sistema debe soportar al menos tres métodos de pago diferentes, incluyendo tarjetas de crédito/débito y al menos una billetera digital popular. Todas las transacciones deben ser encriptadas y cumplir con los estándares de seguridad PCI DSS.</t>
-  </si>
-  <si>
-    <t>El sistema debe calcular automáticamente el costo basado en la duración de la reserva y las tarifas del estacionamiento. Debe considerar tarifas por hora, día y semana según corresponda, y aplicar descuentos si están disponibles.</t>
-  </si>
-  <si>
-    <t>Tras cada pago exitoso, el sistema debe generar un recibo digital detallado en formato PDF, que se enviará por correo electrónico al usuario y estará disponible para descarga en la app por un período de 12 meses.</t>
-  </si>
-  <si>
-    <t>El sistema debe enviar un recordatorio de la reserva 2 horas antes de la hora de llegada estimada, y otro 30 minutos antes, a través de notificaciones push en la app y opcionalmente por SMS.</t>
-  </si>
-  <si>
     <t>Si hay cambios significativos en la disponibilidad del estacionamiento reservado (por ejemplo, cierre inesperado), el sistema debe notificar inmediatamente al usuario y ofrecer alternativas cercanas.</t>
   </si>
   <si>
@@ -677,9 +599,6 @@
     <t>4. Reserva</t>
   </si>
   <si>
-    <t>4.1. Reserva</t>
-  </si>
-  <si>
     <t xml:space="preserve">5. Alerta </t>
   </si>
   <si>
@@ -719,18 +638,6 @@
     <t>Información sobre la política de cancelación y el tiempo límite para cancelar la reserva sin penalización.</t>
   </si>
   <si>
-    <t>Métodos de pago soportados (tarjetas de crédito/débito, billeteras digitales), con transacciones encriptadas cumpliendo con los estándares de seguridad PCI DSS.</t>
-  </si>
-  <si>
-    <t>Tarifas del estacionamiento según la duración de la reserva, incluyendo opciones por hora, día, semana, y la aplicación de descuentos si están disponibles.</t>
-  </si>
-  <si>
-    <t>Recibo digital detallado generado en formato PDF tras un pago exitoso, enviado por correo electrónico y disponible en la app por 12 meses.</t>
-  </si>
-  <si>
-    <t>Recordatorios automáticos enviados al usuario por notificaciones push y opcionalmente por SMS, 2 horas y 30 minutos antes de la hora de llegada estimada.</t>
-  </si>
-  <si>
     <t>Notificaciones automáticas al usuario sobre cambios en la disponibilidad del estacionamiento reservado, incluyendo la oferta de alternativas cercanas.</t>
   </si>
   <si>
@@ -750,6 +657,15 @@
   </si>
   <si>
     <t>|</t>
+  </si>
+  <si>
+    <t>Permitir filtrar los resultados por tipo de estacionamiento (Espacio y Letra).</t>
+  </si>
+  <si>
+    <t>Indicar la hora de inicio</t>
+  </si>
+  <si>
+    <t>Cambios en la disponibilidad del estacionamiento.</t>
   </si>
 </sst>
 </file>
@@ -1489,7 +1405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1693,10 +1609,10 @@
     <xf numFmtId="0" fontId="19" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1731,15 +1647,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1842,9 +1749,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2206,7 +2110,7 @@
       </c>
       <c r="H5" s="89"/>
       <c r="I5" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
@@ -2229,7 +2133,7 @@
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>4</v>
@@ -2253,7 +2157,7 @@
         <v>6</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -2275,8 +2179,8 @@
       <c r="AA6" s="15"/>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A7" s="106" t="s">
-        <v>182</v>
+      <c r="A7" s="103" t="s">
+        <v>156</v>
       </c>
       <c r="B7" s="90" t="s">
         <v>84</v>
@@ -2284,23 +2188,23 @@
       <c r="C7" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="84" t="s">
         <v>85</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="G7" s="58">
         <v>1</v>
       </c>
       <c r="H7" s="82" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -2322,7 +2226,7 @@
       <c r="AA7" s="15"/>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A8" s="107"/>
+      <c r="A8" s="104"/>
       <c r="B8" s="90"/>
       <c r="C8" s="51" t="s">
         <v>81</v>
@@ -2331,19 +2235,19 @@
         <v>88</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="G8" s="58">
         <v>2</v>
       </c>
       <c r="H8" s="60" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -2365,28 +2269,28 @@
       <c r="AA8" s="15"/>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A9" s="107"/>
+      <c r="A9" s="104"/>
       <c r="B9" s="90"/>
       <c r="C9" s="51" t="s">
         <v>83</v>
       </c>
       <c r="D9" s="84" t="s">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G9" s="58">
         <v>3</v>
       </c>
       <c r="H9" s="60" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
@@ -2409,7 +2313,7 @@
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1">
       <c r="A10" s="91" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B10" s="91" t="s">
         <v>77</v>
@@ -2417,23 +2321,23 @@
       <c r="C10" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="86" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="G10" s="58">
         <v>4</v>
       </c>
       <c r="H10" s="60" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
@@ -2464,19 +2368,19 @@
         <v>80</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="G11" s="58">
         <v>5</v>
       </c>
       <c r="H11" s="61" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
@@ -2507,19 +2411,19 @@
         <v>82</v>
       </c>
       <c r="E12" s="56" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G12" s="58">
         <v>6</v>
       </c>
       <c r="H12" s="61" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
@@ -2541,32 +2445,32 @@
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A13" s="108" t="s">
-        <v>184</v>
+      <c r="A13" s="105" t="s">
+        <v>158</v>
       </c>
       <c r="B13" s="96" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D13" s="84" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E13" s="57" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G13" s="58">
         <v>7</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
@@ -2591,25 +2495,25 @@
       <c r="A14" s="93"/>
       <c r="B14" s="96"/>
       <c r="C14" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D14" s="53" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E14" s="57" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="G14" s="58">
         <v>8</v>
       </c>
       <c r="H14" s="61" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -2632,31 +2536,31 @@
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1">
       <c r="A15" s="91" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="B15" s="97" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" s="84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="57" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G15" s="58">
         <v>9</v>
       </c>
       <c r="H15" s="61" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -2681,25 +2585,25 @@
       <c r="A16" s="91"/>
       <c r="B16" s="98"/>
       <c r="C16" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" s="84" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="E16" s="57" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="G16" s="58">
         <v>10</v>
       </c>
       <c r="H16" s="61" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
@@ -2724,25 +2628,25 @@
       <c r="A17" s="91"/>
       <c r="B17" s="98"/>
       <c r="C17" s="51" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
-      <c r="D17" s="86" t="s">
-        <v>98</v>
+      <c r="D17" s="85" t="s">
+        <v>96</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F17" s="55" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="G17" s="59">
         <v>11</v>
       </c>
       <c r="H17" s="61" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
@@ -2767,25 +2671,25 @@
       <c r="A18" s="91"/>
       <c r="B18" s="99"/>
       <c r="C18" s="51" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
-      <c r="D18" s="52" t="s">
-        <v>97</v>
+      <c r="D18" s="84" t="s">
+        <v>95</v>
       </c>
       <c r="E18" s="57" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F18" s="55" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G18" s="59">
         <v>12</v>
       </c>
       <c r="H18" s="61" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
@@ -2807,32 +2711,32 @@
       <c r="AA18" s="15"/>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A19" s="113" t="s">
-        <v>186</v>
+      <c r="A19" s="110" t="s">
+        <v>160</v>
       </c>
       <c r="B19" s="100" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="51" t="s">
-        <v>105</v>
+      <c r="C19" s="51">
+        <v>1.1299999999999999</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="E19" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="F19" s="55" t="s">
-        <v>164</v>
-      </c>
       <c r="G19" s="59">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H19" s="61" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
@@ -2854,28 +2758,28 @@
       <c r="AA19" s="15"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A20" s="113"/>
+      <c r="A20" s="110"/>
       <c r="B20" s="101"/>
-      <c r="C20" s="51" t="s">
-        <v>110</v>
+      <c r="C20" s="51">
+        <v>1.1399999999999999</v>
       </c>
-      <c r="D20" s="52" t="s">
-        <v>101</v>
+      <c r="D20" s="53" t="s">
+        <v>100</v>
       </c>
       <c r="E20" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="F20" s="55" t="s">
-        <v>165</v>
-      </c>
       <c r="G20" s="59">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H20" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
@@ -2897,28 +2801,28 @@
       <c r="AA20" s="15"/>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A21" s="113"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="102"/>
-      <c r="C21" s="51" t="s">
-        <v>111</v>
+      <c r="C21" s="47">
+        <v>1.1499999999999999</v>
       </c>
-      <c r="D21" s="52" t="s">
-        <v>102</v>
+      <c r="D21" s="86" t="s">
+        <v>105</v>
       </c>
       <c r="E21" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="F21" s="55" t="s">
-        <v>166</v>
-      </c>
       <c r="G21" s="59">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H21" s="61" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="I21" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
@@ -2940,32 +2844,32 @@
       <c r="AA21" s="15"/>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A22" s="113" t="s">
-        <v>187</v>
+      <c r="A22" s="110" t="s">
+        <v>112</v>
       </c>
-      <c r="B22" s="103" t="s">
+      <c r="B22" s="94" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="50">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="D22" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="49" t="s">
-        <v>112</v>
+      <c r="E22" s="57" t="s">
+        <v>127</v>
       </c>
-      <c r="D22" s="86" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="57" t="s">
+      <c r="F22" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="F22" s="55" t="s">
-        <v>167</v>
+      <c r="G22" s="59">
+        <v>20</v>
       </c>
-      <c r="G22" s="59">
-        <v>16</v>
-      </c>
-      <c r="H22" s="61" t="s">
-        <v>203</v>
+      <c r="H22" s="83" t="s">
+        <v>176</v>
       </c>
       <c r="I22" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
@@ -2987,28 +2891,28 @@
       <c r="AA22" s="15"/>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A23" s="113"/>
-      <c r="B23" s="104"/>
-      <c r="C23" s="51" t="s">
-        <v>116</v>
+      <c r="A23" s="110"/>
+      <c r="B23" s="95"/>
+      <c r="C23" s="50">
+        <v>1.17</v>
       </c>
-      <c r="D23" s="52" t="s">
-        <v>108</v>
+      <c r="D23" s="84" t="s">
+        <v>107</v>
       </c>
       <c r="E23" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="55" t="s">
-        <v>168</v>
+      <c r="G23" s="59">
+        <v>21</v>
       </c>
-      <c r="G23" s="59">
-        <v>17</v>
-      </c>
-      <c r="H23" s="61" t="s">
-        <v>204</v>
+      <c r="H23" s="83" t="s">
+        <v>177</v>
       </c>
       <c r="I23" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
@@ -3030,28 +2934,28 @@
       <c r="AA23" s="15"/>
     </row>
     <row r="24" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A24" s="113"/>
-      <c r="B24" s="105"/>
-      <c r="C24" s="51" t="s">
-        <v>117</v>
+      <c r="A24" s="110"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="64">
+        <v>1.18</v>
       </c>
-      <c r="D24" s="53" t="s">
-        <v>109</v>
+      <c r="D24" s="65" t="s">
+        <v>108</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="66" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="F24" s="55" t="s">
-        <v>169</v>
+      <c r="G24" s="68">
+        <v>22</v>
       </c>
-      <c r="G24" s="59">
-        <v>18</v>
-      </c>
-      <c r="H24" s="61" t="s">
-        <v>205</v>
+      <c r="H24" s="83" t="s">
+        <v>178</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
@@ -3073,32 +2977,16 @@
       <c r="AA24" s="15"/>
     </row>
     <row r="25" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A25" s="113" t="s">
-        <v>130</v>
-      </c>
-      <c r="B25" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="147" t="s">
-        <v>119</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="55" t="s">
-        <v>170</v>
-      </c>
-      <c r="G25" s="59">
-        <v>19</v>
-      </c>
-      <c r="H25" s="61" t="s">
-        <v>206</v>
-      </c>
+      <c r="A25" s="110"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="63"/>
       <c r="I25" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
@@ -3120,28 +3008,16 @@
       <c r="AA25" s="15"/>
     </row>
     <row r="26" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A26" s="113"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="84" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="F26" s="55" t="s">
-        <v>171</v>
-      </c>
-      <c r="G26" s="59">
-        <v>20</v>
-      </c>
-      <c r="H26" s="83" t="s">
-        <v>207</v>
-      </c>
+      <c r="A26" s="111"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="62"/>
       <c r="I26" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
@@ -3163,28 +3039,16 @@
       <c r="AA26" s="15"/>
     </row>
     <row r="27" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A27" s="113"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="55" t="s">
-        <v>172</v>
-      </c>
-      <c r="G27" s="59">
-        <v>21</v>
-      </c>
-      <c r="H27" s="83" t="s">
-        <v>208</v>
-      </c>
+      <c r="A27" s="111"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="63"/>
       <c r="I27" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
@@ -3206,28 +3070,16 @@
       <c r="AA27" s="15"/>
     </row>
     <row r="28" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A28" s="113"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" s="66" t="s">
-        <v>151</v>
-      </c>
-      <c r="F28" s="67" t="s">
-        <v>173</v>
-      </c>
-      <c r="G28" s="68">
-        <v>22</v>
-      </c>
-      <c r="H28" s="83" t="s">
-        <v>209</v>
-      </c>
+      <c r="A28" s="111"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="63"/>
       <c r="I28" s="58" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -3249,7 +3101,7 @@
       <c r="AA28" s="15"/>
     </row>
     <row r="29" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A29" s="114"/>
+      <c r="A29" s="111"/>
       <c r="B29" s="63"/>
       <c r="C29" s="69"/>
       <c r="D29" s="70"/>
@@ -3278,13 +3130,13 @@
       <c r="AA29" s="15"/>
     </row>
     <row r="30" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A30" s="114"/>
+      <c r="A30" s="111"/>
       <c r="B30" s="63"/>
       <c r="C30" s="69"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
       <c r="H30" s="62"/>
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
@@ -3307,13 +3159,13 @@
       <c r="AA30" s="15"/>
     </row>
     <row r="31" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A31" s="114"/>
-      <c r="B31" s="63"/>
+      <c r="A31" s="109"/>
+      <c r="B31" s="73"/>
       <c r="C31" s="69"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
       <c r="H31" s="63"/>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
@@ -3336,13 +3188,13 @@
       <c r="AA31" s="15"/>
     </row>
     <row r="32" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A32" s="114"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="63"/>
       <c r="C32" s="69"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
       <c r="H32" s="63"/>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
@@ -3365,13 +3217,13 @@
       <c r="AA32" s="15"/>
     </row>
     <row r="33" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A33" s="114"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="63"/>
       <c r="C33" s="69"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="75"/>
       <c r="H33" s="63"/>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
@@ -3394,14 +3246,14 @@
       <c r="AA33" s="15"/>
     </row>
     <row r="34" spans="1:27" ht="15" customHeight="1">
-      <c r="A34" s="112"/>
-      <c r="B34" s="73"/>
+      <c r="A34" s="107"/>
+      <c r="B34" s="63"/>
       <c r="C34" s="69"/>
       <c r="D34" s="74"/>
       <c r="E34" s="75"/>
-      <c r="F34" s="74"/>
+      <c r="F34" s="75"/>
       <c r="G34" s="75"/>
-      <c r="H34" s="62"/>
+      <c r="H34" s="63"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
@@ -3423,12 +3275,12 @@
       <c r="AA34" s="4"/>
     </row>
     <row r="35" spans="1:27" ht="15" customHeight="1">
-      <c r="A35" s="110"/>
+      <c r="A35" s="107"/>
       <c r="B35" s="63"/>
       <c r="C35" s="69"/>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
-      <c r="F35" s="74"/>
+      <c r="F35" s="75"/>
       <c r="G35" s="75"/>
       <c r="H35" s="63"/>
       <c r="I35" s="4"/>
@@ -3452,14 +3304,14 @@
       <c r="AA35" s="4"/>
     </row>
     <row r="36" spans="1:27" ht="15" customHeight="1">
-      <c r="A36" s="110"/>
+      <c r="A36" s="108"/>
       <c r="B36" s="63"/>
       <c r="C36" s="69"/>
       <c r="D36" s="74"/>
       <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="63"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="62"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
@@ -3481,13 +3333,13 @@
       <c r="AA36" s="4"/>
     </row>
     <row r="37" spans="1:27" ht="15" customHeight="1">
-      <c r="A37" s="110"/>
-      <c r="B37" s="63"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="73"/>
       <c r="C37" s="69"/>
       <c r="D37" s="74"/>
       <c r="E37" s="75"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
       <c r="H37" s="63"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -3510,13 +3362,13 @@
       <c r="AA37" s="4"/>
     </row>
     <row r="38" spans="1:27" ht="15" customHeight="1">
-      <c r="A38" s="110"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="63"/>
       <c r="C38" s="69"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="74"/>
       <c r="H38" s="63"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -3539,13 +3391,13 @@
       <c r="AA38" s="4"/>
     </row>
     <row r="39" spans="1:27" ht="15" customHeight="1">
-      <c r="A39" s="111"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="63"/>
       <c r="C39" s="69"/>
       <c r="D39" s="74"/>
       <c r="E39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="74"/>
       <c r="H39" s="63"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -3568,14 +3420,14 @@
       <c r="AA39" s="4"/>
     </row>
     <row r="40" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A40" s="109"/>
-      <c r="B40" s="73"/>
+      <c r="A40" s="107"/>
+      <c r="B40" s="63"/>
       <c r="C40" s="69"/>
       <c r="D40" s="74"/>
       <c r="E40" s="75"/>
       <c r="F40" s="74"/>
       <c r="G40" s="74"/>
-      <c r="H40" s="62"/>
+      <c r="H40" s="79"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
@@ -3597,14 +3449,14 @@
       <c r="AA40" s="4"/>
     </row>
     <row r="41" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A41" s="110"/>
-      <c r="B41" s="63"/>
+      <c r="A41" s="107"/>
+      <c r="B41" s="73"/>
       <c r="C41" s="69"/>
       <c r="D41" s="74"/>
       <c r="E41" s="75"/>
       <c r="F41" s="74"/>
       <c r="G41" s="74"/>
-      <c r="H41" s="63"/>
+      <c r="H41" s="79"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
@@ -3626,14 +3478,14 @@
       <c r="AA41" s="4"/>
     </row>
     <row r="42" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A42" s="110"/>
+      <c r="A42" s="107"/>
       <c r="B42" s="63"/>
       <c r="C42" s="69"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="78"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
       <c r="G42" s="74"/>
-      <c r="H42" s="63"/>
+      <c r="H42" s="79"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
@@ -3655,14 +3507,14 @@
       <c r="AA42" s="4"/>
     </row>
     <row r="43" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A43" s="110"/>
+      <c r="A43" s="107"/>
       <c r="B43" s="63"/>
       <c r="C43" s="69"/>
       <c r="D43" s="74"/>
       <c r="E43" s="75"/>
       <c r="F43" s="74"/>
       <c r="G43" s="74"/>
-      <c r="H43" s="63"/>
+      <c r="H43" s="80"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
@@ -3684,14 +3536,14 @@
       <c r="AA43" s="4"/>
     </row>
     <row r="44" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A44" s="110"/>
+      <c r="A44" s="106"/>
       <c r="B44" s="73"/>
       <c r="C44" s="69"/>
       <c r="D44" s="74"/>
       <c r="E44" s="75"/>
       <c r="F44" s="74"/>
       <c r="G44" s="74"/>
-      <c r="H44" s="79"/>
+      <c r="H44" s="63"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
@@ -3713,14 +3565,14 @@
       <c r="AA44" s="4"/>
     </row>
     <row r="45" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A45" s="110"/>
+      <c r="A45" s="107"/>
       <c r="B45" s="63"/>
       <c r="C45" s="69"/>
       <c r="D45" s="74"/>
       <c r="E45" s="75"/>
       <c r="F45" s="74"/>
       <c r="G45" s="74"/>
-      <c r="H45" s="79"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
@@ -3742,14 +3594,14 @@
       <c r="AA45" s="4"/>
     </row>
     <row r="46" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A46" s="110"/>
+      <c r="A46" s="107"/>
       <c r="B46" s="63"/>
       <c r="C46" s="69"/>
       <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
+      <c r="E46" s="75"/>
       <c r="F46" s="74"/>
       <c r="G46" s="74"/>
-      <c r="H46" s="79"/>
+      <c r="H46" s="63"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
@@ -3771,14 +3623,14 @@
       <c r="AA46" s="4"/>
     </row>
     <row r="47" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A47" s="109"/>
-      <c r="B47" s="73"/>
+      <c r="A47" s="107"/>
+      <c r="B47" s="63"/>
       <c r="C47" s="69"/>
       <c r="D47" s="74"/>
       <c r="E47" s="75"/>
       <c r="F47" s="74"/>
       <c r="G47" s="74"/>
-      <c r="H47" s="80"/>
+      <c r="H47" s="63"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
@@ -3800,7 +3652,7 @@
       <c r="AA47" s="4"/>
     </row>
     <row r="48" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A48" s="110"/>
+      <c r="A48" s="107"/>
       <c r="B48" s="63"/>
       <c r="C48" s="69"/>
       <c r="D48" s="74"/>
@@ -3829,7 +3681,7 @@
       <c r="AA48" s="4"/>
     </row>
     <row r="49" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A49" s="110"/>
+      <c r="A49" s="107"/>
       <c r="B49" s="63"/>
       <c r="C49" s="69"/>
       <c r="D49" s="74"/>
@@ -3858,7 +3710,7 @@
       <c r="AA49" s="4"/>
     </row>
     <row r="50" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A50" s="110"/>
+      <c r="A50" s="107"/>
       <c r="B50" s="63"/>
       <c r="C50" s="69"/>
       <c r="D50" s="74"/>
@@ -3887,7 +3739,7 @@
       <c r="AA50" s="4"/>
     </row>
     <row r="51" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A51" s="110"/>
+      <c r="A51" s="107"/>
       <c r="B51" s="63"/>
       <c r="C51" s="69"/>
       <c r="D51" s="74"/>
@@ -3916,7 +3768,7 @@
       <c r="AA51" s="4"/>
     </row>
     <row r="52" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A52" s="110"/>
+      <c r="A52" s="107"/>
       <c r="B52" s="63"/>
       <c r="C52" s="69"/>
       <c r="D52" s="74"/>
@@ -3945,8 +3797,8 @@
       <c r="AA52" s="4"/>
     </row>
     <row r="53" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A53" s="110"/>
-      <c r="B53" s="63"/>
+      <c r="A53" s="107"/>
+      <c r="B53" s="73"/>
       <c r="C53" s="69"/>
       <c r="D53" s="74"/>
       <c r="E53" s="75"/>
@@ -3974,7 +3826,7 @@
       <c r="AA53" s="4"/>
     </row>
     <row r="54" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A54" s="110"/>
+      <c r="A54" s="107"/>
       <c r="B54" s="63"/>
       <c r="C54" s="69"/>
       <c r="D54" s="74"/>
@@ -4003,7 +3855,7 @@
       <c r="AA54" s="4"/>
     </row>
     <row r="55" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A55" s="110"/>
+      <c r="A55" s="107"/>
       <c r="B55" s="63"/>
       <c r="C55" s="69"/>
       <c r="D55" s="74"/>
@@ -4032,14 +3884,13 @@
       <c r="AA55" s="4"/>
     </row>
     <row r="56" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A56" s="110"/>
-      <c r="B56" s="73"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="74"/>
-      <c r="H56" s="63"/>
+      <c r="A56" s="108"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="5"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="7"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
@@ -4061,14 +3912,13 @@
       <c r="AA56" s="4"/>
     </row>
     <row r="57" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A57" s="110"/>
-      <c r="B57" s="63"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="63"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="5"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="7"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
@@ -4090,14 +3940,14 @@
       <c r="AA57" s="4"/>
     </row>
     <row r="58" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A58" s="110"/>
-      <c r="B58" s="63"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="75"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="63"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="7"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
@@ -4119,14 +3969,14 @@
       <c r="AA58" s="4"/>
     </row>
     <row r="59" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A59" s="111"/>
-      <c r="B59" s="63"/>
-      <c r="C59" s="69"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="75"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="63"/>
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="7"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
@@ -4151,6 +4001,7 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
+      <c r="D60" s="4"/>
       <c r="E60" s="6"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -4179,6 +4030,7 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
+      <c r="D61" s="4"/>
       <c r="E61" s="6"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -4236,7 +4088,6 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="4"/>
       <c r="E63" s="6"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
@@ -4265,7 +4116,6 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="4"/>
       <c r="E64" s="6"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
@@ -4294,7 +4144,6 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
-      <c r="D65" s="4"/>
       <c r="E65" s="6"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
@@ -4352,6 +4201,7 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="5"/>
+      <c r="D67" s="4"/>
       <c r="E67" s="6"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
@@ -4380,6 +4230,7 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="5"/>
+      <c r="D68" s="4"/>
       <c r="E68" s="6"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -4408,6 +4259,7 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="5"/>
+      <c r="D69" s="4"/>
       <c r="E69" s="6"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -8698,12 +8550,9 @@
     <row r="217" spans="1:27" ht="14.25" customHeight="1">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
-      <c r="C217" s="5"/>
-      <c r="D217" s="4"/>
-      <c r="E217" s="6"/>
-      <c r="F217" s="4"/>
-      <c r="G217" s="4"/>
-      <c r="H217" s="7"/>
+      <c r="C217" s="1"/>
+      <c r="E217" s="2"/>
+      <c r="H217" s="3"/>
       <c r="I217" s="4"/>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
@@ -8725,14 +8574,9 @@
       <c r="AA217" s="4"/>
     </row>
     <row r="218" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A218" s="4"/>
-      <c r="B218" s="4"/>
-      <c r="C218" s="5"/>
-      <c r="D218" s="4"/>
-      <c r="E218" s="6"/>
-      <c r="F218" s="4"/>
-      <c r="G218" s="4"/>
-      <c r="H218" s="7"/>
+      <c r="C218" s="1"/>
+      <c r="E218" s="2"/>
+      <c r="H218" s="3"/>
       <c r="I218" s="4"/>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
@@ -8754,14 +8598,9 @@
       <c r="AA218" s="4"/>
     </row>
     <row r="219" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A219" s="4"/>
-      <c r="B219" s="4"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="4"/>
-      <c r="E219" s="6"/>
-      <c r="F219" s="4"/>
-      <c r="G219" s="4"/>
-      <c r="H219" s="7"/>
+      <c r="C219" s="1"/>
+      <c r="E219" s="2"/>
+      <c r="H219" s="3"/>
       <c r="I219" s="4"/>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
@@ -8783,14 +8622,9 @@
       <c r="AA219" s="4"/>
     </row>
     <row r="220" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A220" s="4"/>
-      <c r="B220" s="4"/>
-      <c r="C220" s="5"/>
-      <c r="D220" s="4"/>
-      <c r="E220" s="6"/>
-      <c r="F220" s="4"/>
-      <c r="G220" s="4"/>
-      <c r="H220" s="7"/>
+      <c r="C220" s="1"/>
+      <c r="E220" s="2"/>
+      <c r="H220" s="3"/>
       <c r="I220" s="4"/>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
@@ -12691,44 +12525,26 @@
       <c r="E996" s="2"/>
       <c r="H996" s="3"/>
     </row>
-    <row r="997" spans="3:8" ht="15.75" customHeight="1">
-      <c r="C997" s="1"/>
-      <c r="E997" s="2"/>
-      <c r="H997" s="3"/>
-    </row>
-    <row r="998" spans="3:8" ht="15.75" customHeight="1">
-      <c r="C998" s="1"/>
-      <c r="E998" s="2"/>
-      <c r="H998" s="3"/>
-    </row>
-    <row r="999" spans="3:8" ht="15.75" customHeight="1">
-      <c r="C999" s="1"/>
-      <c r="E999" s="2"/>
-      <c r="H999" s="3"/>
-    </row>
-    <row r="1000" spans="3:8" ht="15.75" customHeight="1">
-      <c r="C1000" s="1"/>
-      <c r="E1000" s="2"/>
-      <c r="H1000" s="3"/>
-    </row>
+    <row r="997" spans="3:8" ht="15.75" customHeight="1"/>
+    <row r="998" spans="3:8" ht="15.75" customHeight="1"/>
+    <row r="999" spans="3:8" ht="15.75" customHeight="1"/>
+    <row r="1000" spans="3:8" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="19">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A59"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A44:A56"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A30"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="B22:B25"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B22:B24"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
@@ -12756,15 +12572,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="117"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="114"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -12786,7 +12602,7 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="115" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="89"/>
@@ -12819,7 +12635,7 @@
       <c r="A3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="115" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="89"/>
@@ -12855,16 +12671,16 @@
       <c r="A4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="119" t="s">
-        <v>174</v>
+      <c r="B4" s="116" t="s">
+        <v>148</v>
       </c>
       <c r="C4" s="89"/>
       <c r="D4" s="89"/>
       <c r="E4" s="88"/>
-      <c r="F4" s="120" t="s">
+      <c r="F4" s="117" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="123" t="s">
+      <c r="G4" s="120" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="4"/>
@@ -12891,12 +12707,12 @@
       <c r="A5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="119"/>
+      <c r="B5" s="116"/>
       <c r="C5" s="89"/>
       <c r="D5" s="89"/>
       <c r="E5" s="88"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="110"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="107"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -12921,12 +12737,12 @@
       <c r="A6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="119"/>
+      <c r="B6" s="116"/>
       <c r="C6" s="89"/>
       <c r="D6" s="89"/>
       <c r="E6" s="88"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="110"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="107"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -12951,12 +12767,12 @@
       <c r="A7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="119"/>
+      <c r="B7" s="116"/>
       <c r="C7" s="89"/>
       <c r="D7" s="89"/>
       <c r="E7" s="88"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="110"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="107"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -12981,16 +12797,16 @@
       <c r="A8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="124" t="s">
-        <v>175</v>
+      <c r="B8" s="121" t="s">
+        <v>149</v>
       </c>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="127" t="s">
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="123" t="s">
+      <c r="G8" s="120" t="s">
         <v>19</v>
       </c>
       <c r="H8" s="4"/>
@@ -13017,12 +12833,12 @@
       <c r="A9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="119"/>
+      <c r="B9" s="116"/>
       <c r="C9" s="89"/>
       <c r="D9" s="89"/>
       <c r="E9" s="88"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="110"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="107"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -13047,16 +12863,16 @@
       <c r="A10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="119" t="s">
-        <v>176</v>
+      <c r="B10" s="116" t="s">
+        <v>150</v>
       </c>
       <c r="C10" s="89"/>
       <c r="D10" s="89"/>
       <c r="E10" s="88"/>
-      <c r="F10" s="120" t="s">
+      <c r="F10" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="123" t="s">
+      <c r="G10" s="120" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="4"/>
@@ -13083,12 +12899,12 @@
       <c r="A11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="119"/>
+      <c r="B11" s="116"/>
       <c r="C11" s="89"/>
       <c r="D11" s="89"/>
       <c r="E11" s="88"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="110"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="107"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -13113,12 +12929,12 @@
       <c r="A12" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="119"/>
+      <c r="B12" s="116"/>
       <c r="C12" s="89"/>
       <c r="D12" s="89"/>
       <c r="E12" s="88"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="110"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="107"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -13143,12 +12959,12 @@
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="119"/>
+      <c r="B13" s="116"/>
       <c r="C13" s="89"/>
       <c r="D13" s="89"/>
       <c r="E13" s="88"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="110"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="107"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -13173,16 +12989,16 @@
       <c r="A14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="119" t="s">
-        <v>177</v>
+      <c r="B14" s="116" t="s">
+        <v>151</v>
       </c>
       <c r="C14" s="89"/>
       <c r="D14" s="89"/>
       <c r="E14" s="88"/>
-      <c r="F14" s="127" t="s">
+      <c r="F14" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="123" t="s">
+      <c r="G14" s="120" t="s">
         <v>29</v>
       </c>
       <c r="I14" s="4"/>
@@ -13208,12 +13024,12 @@
       <c r="A15" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="119"/>
+      <c r="B15" s="116"/>
       <c r="C15" s="89"/>
       <c r="D15" s="89"/>
       <c r="E15" s="88"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="110"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="107"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -13238,16 +13054,16 @@
       <c r="A16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="119" t="s">
-        <v>181</v>
+      <c r="B16" s="116" t="s">
+        <v>155</v>
       </c>
       <c r="C16" s="89"/>
       <c r="D16" s="89"/>
       <c r="E16" s="88"/>
-      <c r="F16" s="120" t="s">
+      <c r="F16" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="123" t="s">
+      <c r="G16" s="120" t="s">
         <v>33</v>
       </c>
       <c r="H16" s="4"/>
@@ -13274,12 +13090,12 @@
       <c r="A17" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="119"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="89"/>
       <c r="D17" s="89"/>
       <c r="E17" s="88"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="110"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="107"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
@@ -13304,16 +13120,16 @@
       <c r="A18" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="119" t="s">
-        <v>179</v>
+      <c r="B18" s="116" t="s">
+        <v>153</v>
       </c>
       <c r="C18" s="89"/>
       <c r="D18" s="89"/>
       <c r="E18" s="88"/>
-      <c r="F18" s="127" t="s">
+      <c r="F18" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="123" t="s">
+      <c r="G18" s="120" t="s">
         <v>37</v>
       </c>
       <c r="H18" s="4"/>
@@ -13340,12 +13156,12 @@
       <c r="A19" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="119"/>
+      <c r="B19" s="116"/>
       <c r="C19" s="89"/>
       <c r="D19" s="89"/>
       <c r="E19" s="88"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="110"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="107"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -13370,12 +13186,12 @@
       <c r="A20" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="119"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="89"/>
       <c r="D20" s="89"/>
       <c r="E20" s="88"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="110"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="107"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -13400,16 +13216,16 @@
       <c r="A21" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="119" t="s">
-        <v>180</v>
+      <c r="B21" s="116" t="s">
+        <v>154</v>
       </c>
       <c r="C21" s="89"/>
       <c r="D21" s="89"/>
       <c r="E21" s="88"/>
-      <c r="F21" s="120" t="s">
+      <c r="F21" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="123" t="s">
+      <c r="G21" s="120" t="s">
         <v>42</v>
       </c>
       <c r="I21" s="4"/>
@@ -13435,12 +13251,12 @@
       <c r="A22" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="119"/>
+      <c r="B22" s="116"/>
       <c r="C22" s="89"/>
       <c r="D22" s="89"/>
       <c r="E22" s="88"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="110"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="107"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -13465,16 +13281,16 @@
       <c r="A23" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="119" t="s">
-        <v>178</v>
+      <c r="B23" s="116" t="s">
+        <v>152</v>
       </c>
       <c r="C23" s="89"/>
       <c r="D23" s="89"/>
       <c r="E23" s="88"/>
-      <c r="F23" s="127" t="s">
+      <c r="F23" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="123" t="s">
+      <c r="G23" s="120" t="s">
         <v>46</v>
       </c>
       <c r="H23" s="4"/>
@@ -13501,12 +13317,12 @@
       <c r="A24" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="119"/>
+      <c r="B24" s="116"/>
       <c r="C24" s="89"/>
       <c r="D24" s="89"/>
       <c r="E24" s="88"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="110"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="107"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -22305,36 +22121,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:111" ht="21.75" customHeight="1">
-      <c r="A1" s="128"/>
-      <c r="B1" s="129"/>
-      <c r="C1" s="133" t="s">
+      <c r="A1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="134" t="s">
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="131" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="136"/>
-      <c r="U1" s="137" t="s">
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="V1" s="138"/>
-      <c r="W1" s="138"/>
-      <c r="X1" s="139"/>
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="136"/>
       <c r="Y1" s="23"/>
       <c r="Z1" s="23"/>
       <c r="AA1" s="23"/>
@@ -22424,8 +22240,8 @@
       <c r="DG1" s="24"/>
     </row>
     <row r="2" spans="1:111" ht="18.75" customHeight="1">
-      <c r="A2" s="129"/>
-      <c r="B2" s="129"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
       <c r="C2" s="25" t="s">
         <v>51</v>
       </c>
@@ -22447,25 +22263,25 @@
       <c r="I2" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="140" t="s">
+      <c r="J2" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="135"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="140" t="s">
+      <c r="K2" s="132"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="137" t="s">
         <v>59</v>
       </c>
-      <c r="N2" s="136"/>
-      <c r="O2" s="140" t="s">
+      <c r="N2" s="133"/>
+      <c r="O2" s="137" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="140" t="s">
+      <c r="P2" s="132"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="135"/>
-      <c r="T2" s="136"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="133"/>
       <c r="U2" s="27" t="s">
         <v>62</v>
       </c>
@@ -22567,7 +22383,7 @@
       <c r="DG2" s="30"/>
     </row>
     <row r="3" spans="1:111" ht="21" customHeight="1">
-      <c r="A3" s="130" t="s">
+      <c r="A3" s="127" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -22582,21 +22398,21 @@
       <c r="G3" s="33"/>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
-      <c r="J3" s="141" t="s">
+      <c r="J3" s="138" t="s">
         <v>68</v>
       </c>
-      <c r="K3" s="142"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="144"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="141" t="s">
+      <c r="K3" s="139"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="138" t="s">
         <v>68</v>
       </c>
-      <c r="P3" s="142"/>
-      <c r="Q3" s="143"/>
-      <c r="R3" s="141"/>
-      <c r="S3" s="142"/>
-      <c r="T3" s="142"/>
+      <c r="P3" s="139"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="139"/>
+      <c r="T3" s="139"/>
       <c r="U3" s="34"/>
       <c r="V3" s="34"/>
       <c r="W3" s="34"/>
@@ -22690,7 +22506,7 @@
       <c r="DG3" s="15"/>
     </row>
     <row r="4" spans="1:111" ht="21" customHeight="1">
-      <c r="A4" s="131"/>
+      <c r="A4" s="128"/>
       <c r="B4" s="35" t="s">
         <v>69</v>
       </c>
@@ -22705,17 +22521,17 @@
       <c r="G4" s="37"/>
       <c r="H4" s="37"/>
       <c r="I4" s="37"/>
-      <c r="J4" s="145"/>
+      <c r="J4" s="142"/>
       <c r="K4" s="89"/>
       <c r="L4" s="88"/>
-      <c r="M4" s="118" t="s">
+      <c r="M4" s="115" t="s">
         <v>68</v>
       </c>
       <c r="N4" s="88"/>
-      <c r="O4" s="145"/>
+      <c r="O4" s="142"/>
       <c r="P4" s="89"/>
       <c r="Q4" s="88"/>
-      <c r="R4" s="145"/>
+      <c r="R4" s="142"/>
       <c r="S4" s="89"/>
       <c r="T4" s="89"/>
       <c r="U4" s="34"/>
@@ -22811,7 +22627,7 @@
       <c r="DG4" s="15"/>
     </row>
     <row r="5" spans="1:111" ht="21" customHeight="1">
-      <c r="A5" s="131"/>
+      <c r="A5" s="128"/>
       <c r="B5" s="35" t="s">
         <v>70</v>
       </c>
@@ -22824,17 +22640,17 @@
       <c r="G5" s="38"/>
       <c r="H5" s="38"/>
       <c r="I5" s="38"/>
-      <c r="J5" s="145"/>
+      <c r="J5" s="142"/>
       <c r="K5" s="89"/>
       <c r="L5" s="88"/>
-      <c r="M5" s="118" t="s">
+      <c r="M5" s="115" t="s">
         <v>68</v>
       </c>
       <c r="N5" s="88"/>
-      <c r="O5" s="145"/>
+      <c r="O5" s="142"/>
       <c r="P5" s="89"/>
       <c r="Q5" s="88"/>
-      <c r="R5" s="145"/>
+      <c r="R5" s="142"/>
       <c r="S5" s="89"/>
       <c r="T5" s="89"/>
       <c r="U5" s="34"/>
@@ -22930,7 +22746,7 @@
       <c r="DG5" s="15"/>
     </row>
     <row r="6" spans="1:111" ht="21" customHeight="1">
-      <c r="A6" s="131"/>
+      <c r="A6" s="128"/>
       <c r="B6" s="35" t="s">
         <v>71</v>
       </c>
@@ -22943,17 +22759,17 @@
       <c r="G6" s="38"/>
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
-      <c r="J6" s="145"/>
+      <c r="J6" s="142"/>
       <c r="K6" s="89"/>
       <c r="L6" s="88"/>
-      <c r="M6" s="118" t="s">
+      <c r="M6" s="115" t="s">
         <v>68</v>
       </c>
       <c r="N6" s="88"/>
-      <c r="O6" s="145"/>
+      <c r="O6" s="142"/>
       <c r="P6" s="89"/>
       <c r="Q6" s="88"/>
-      <c r="R6" s="145"/>
+      <c r="R6" s="142"/>
       <c r="S6" s="89"/>
       <c r="T6" s="89"/>
       <c r="U6" s="34"/>
@@ -23049,7 +22865,7 @@
       <c r="DG6" s="15"/>
     </row>
     <row r="7" spans="1:111" ht="21" customHeight="1">
-      <c r="A7" s="131"/>
+      <c r="A7" s="128"/>
       <c r="B7" s="35" t="s">
         <v>72</v>
       </c>
@@ -23062,17 +22878,17 @@
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
-      <c r="J7" s="145"/>
+      <c r="J7" s="142"/>
       <c r="K7" s="89"/>
       <c r="L7" s="88"/>
-      <c r="M7" s="118" t="s">
+      <c r="M7" s="115" t="s">
         <v>68</v>
       </c>
       <c r="N7" s="88"/>
-      <c r="O7" s="145"/>
+      <c r="O7" s="142"/>
       <c r="P7" s="89"/>
       <c r="Q7" s="88"/>
-      <c r="R7" s="145"/>
+      <c r="R7" s="142"/>
       <c r="S7" s="89"/>
       <c r="T7" s="89"/>
       <c r="U7" s="34"/>
@@ -23168,7 +22984,7 @@
       <c r="DG7" s="15"/>
     </row>
     <row r="8" spans="1:111" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
+      <c r="A8" s="128"/>
       <c r="B8" s="35" t="s">
         <v>73</v>
       </c>
@@ -23181,17 +22997,17 @@
         <v>68</v>
       </c>
       <c r="I8" s="38"/>
-      <c r="J8" s="145"/>
+      <c r="J8" s="142"/>
       <c r="K8" s="89"/>
       <c r="L8" s="88"/>
-      <c r="M8" s="118" t="s">
+      <c r="M8" s="115" t="s">
         <v>68</v>
       </c>
       <c r="N8" s="88"/>
-      <c r="O8" s="146"/>
+      <c r="O8" s="143"/>
       <c r="P8" s="89"/>
       <c r="Q8" s="88"/>
-      <c r="R8" s="146"/>
+      <c r="R8" s="143"/>
       <c r="S8" s="89"/>
       <c r="T8" s="89"/>
       <c r="U8" s="34"/>
@@ -23287,7 +23103,7 @@
       <c r="DG8" s="15"/>
     </row>
     <row r="9" spans="1:111" ht="21" customHeight="1">
-      <c r="A9" s="132"/>
+      <c r="A9" s="129"/>
       <c r="B9" s="35" t="s">
         <v>74</v>
       </c>
@@ -23300,15 +23116,15 @@
       <c r="I9" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="145"/>
+      <c r="J9" s="142"/>
       <c r="K9" s="89"/>
       <c r="L9" s="88"/>
-      <c r="M9" s="118"/>
+      <c r="M9" s="115"/>
       <c r="N9" s="88"/>
-      <c r="O9" s="118"/>
+      <c r="O9" s="115"/>
       <c r="P9" s="89"/>
       <c r="Q9" s="88"/>
-      <c r="R9" s="118" t="s">
+      <c r="R9" s="115" t="s">
         <v>68</v>
       </c>
       <c r="S9" s="89"/>
